--- a/КПП/Том СКУД КПП/Журнал входного контроля СКУД КПП.xlsx
+++ b/КПП/Том СКУД КПП/Журнал входного контроля СКУД КПП.xlsx
@@ -508,7 +508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K50"/>
+  <dimension ref="A1:K51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1632,12 +1632,12 @@
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>Контроллер доступа, С2000-2 (поз. ARK)</t>
+          <t>Кнопка аварийного открытия (разблокировки) двери, ST-ER115 (поз. EDU)</t>
         </is>
       </c>
       <c r="D34" s="11" t="inlineStr">
         <is>
-          <t>Болид</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E34" s="10" t="inlineStr">
@@ -1646,7 +1646,7 @@
         </is>
       </c>
       <c r="F34" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G34" s="11" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>Резервированный источник питания, РИП-12 исп.17 (поз. UG6)</t>
+          <t>Контроллер доступа, С2000-2 (поз. ARK)</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="F35" s="10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G35" s="11" t="inlineStr">
         <is>
@@ -1738,12 +1738,12 @@
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
-          <t>Батарея аккумуляторная 12 В 18 А·ч (в РИП-12, UG6), DT 12В 18Ач</t>
+          <t>Резервированный источник питания, РИП-12 исп.17 (поз. UG6)</t>
         </is>
       </c>
       <c r="D36" s="11" t="inlineStr">
         <is>
-          <t>Delta</t>
+          <t>Болид</t>
         </is>
       </c>
       <c r="E36" s="10" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>Монитор видеодомофона цветной, DS-D100MF (поз. VS)</t>
+          <t>Батарея аккумуляторная 12 В 18 А·ч (в РИП-12, UG6), DT 12В 18Ач</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Delta</t>
         </is>
       </c>
       <c r="E37" s="10" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
-          <t>Видеодомофонная вызывная панель цветная, DS-D100P (поз. AVD)</t>
+          <t>Монитор видеодомофона цветной, DS-D100MF (поз. VS)</t>
         </is>
       </c>
       <c r="D38" s="11" t="inlineStr">
@@ -1858,7 +1858,7 @@
         </is>
       </c>
       <c r="F38" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G38" s="11" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>Рабочее место: мини-ПК CHUWI AuBox X, мониторы Acer SB322QAbi 31,5" (2 шт.) с креплениями DEXP MB32-W01, клавиатура и мышь Defender C-511, преобразователь USB-RS485 (поз. АРК)</t>
+          <t>Видеодомофонная вызывная панель цветная, DS-D100P (поз. AVD)</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="F39" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G39" s="11" t="inlineStr">
         <is>
@@ -1950,12 +1950,12 @@
       </c>
       <c r="C40" s="11" t="inlineStr">
         <is>
-          <t>Привод электромеханический для распашных ворот, CAME A5000A (комплект ATI5000A) (поз. М)</t>
+          <t>Рабочее место: мини-ПК CHUWI AuBox X, мониторы Acer SB322QAbi 31,5" (2 шт.) с креплениями DEXP MB32-W01, клавиатура и мышь Defender C-511, преобразователь USB-RS485 (поз. АРК)</t>
         </is>
       </c>
       <c r="D40" s="11" t="inlineStr">
         <is>
-          <t>CAME</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E40" s="10" t="inlineStr">
@@ -1964,7 +1964,7 @@
         </is>
       </c>
       <c r="F40" s="10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G40" s="11" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>Блок управления электромеханическим приводом ворот (комплектный), CAME ZF1N (поз. БУ)</t>
+          <t>Привод электромеханический для распашных ворот, CAME A5000A (комплект ATI5000A) (поз. М)</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="F41" s="10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G41" s="11" t="inlineStr">
         <is>
@@ -2056,12 +2056,12 @@
       </c>
       <c r="C42" s="11" t="inlineStr">
         <is>
-          <t>Пост остановки колесного автотранспорта, Дорожный блокиратор механический 3,5 м (поз. PK)</t>
+          <t>Блок управления электромеханическим приводом ворот (комплектный), CAME ZF1N (поз. БУ)</t>
         </is>
       </c>
       <c r="D42" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CAME</t>
         </is>
       </c>
       <c r="E42" s="10" t="inlineStr">
@@ -2070,7 +2070,7 @@
         </is>
       </c>
       <c r="F42" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G42" s="11" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>Блок управления противотаранным устройством (комплектный) (поз. БУпту)</t>
+          <t>Пост остановки колесного автотранспорта, Дорожный блокиратор механический 3,5 м (поз. PK)</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="C44" s="11" t="inlineStr">
         <is>
-          <t>Пульт управления ПТУ (комплектный) (поз. П)</t>
+          <t>Блок управления противотаранным устройством (комплектный) (поз. БУпту)</t>
         </is>
       </c>
       <c r="D44" s="11" t="inlineStr">
@@ -2204,49 +2204,102 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="12" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="10" t="n">
+        <v>29</v>
+      </c>
+      <c r="B45" s="10" t="inlineStr">
+        <is>
+          <t>16.10.2026</t>
+        </is>
+      </c>
+      <c r="C45" s="11" t="inlineStr">
+        <is>
+          <t>Пульт управления ПТУ (комплектный) (поз. П)</t>
+        </is>
+      </c>
+      <c r="D45" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E45" s="10" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="F45" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" s="11" t="inlineStr">
+        <is>
+          <t>Паспорт (руководство по эксплуатации) изготовителя</t>
+        </is>
+      </c>
+      <c r="H45" s="11" t="inlineStr">
+        <is>
+          <t>Внешний осмотр, маркировка, комплектность — без замечаний. Паспорт изготовителя в наличии (оригинал).</t>
+        </is>
+      </c>
+      <c r="I45" s="11" t="inlineStr">
+        <is>
+          <t>Соответствует. Допущено к применению</t>
+        </is>
+      </c>
+      <c r="J45" s="11" t="inlineStr">
+        <is>
+          <t>Иванчук М.В.</t>
+        </is>
+      </c>
+      <c r="K45" s="11" t="inlineStr">
+        <is>
+          <t>ИД лист 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="12" t="inlineStr">
         <is>
           <t>Ответственный за входной контроль (лицо, выполняющее работы)</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="13" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="13" t="inlineStr">
         <is>
           <t>начальник отдела систем технической безопасности ООО «АльтЭн» Иванчук М.В.</t>
         </is>
       </c>
-      <c r="G47" s="14" t="inlineStr">
+      <c r="G48" s="14" t="inlineStr">
         <is>
           <t>____________________ (подпись)</t>
         </is>
       </c>
-      <c r="I47" s="14" t="inlineStr">
+      <c r="I48" s="14" t="inlineStr">
         <is>
           <t>«____» ____________ 2026 г.</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="12" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="12" t="inlineStr">
         <is>
           <t>Представитель лица, осуществляющего строительство</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="13" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="13" t="inlineStr">
         <is>
           <t>руководитель проекта Белоногов И.Ю.</t>
         </is>
       </c>
-      <c r="G50" s="14" t="inlineStr">
+      <c r="G51" s="14" t="inlineStr">
         <is>
           <t>____________________ (подпись)</t>
         </is>
       </c>
-      <c r="I50" s="14" t="inlineStr">
+      <c r="I51" s="14" t="inlineStr">
         <is>
           <t>«____» ____________ 2026 г.</t>
         </is>
@@ -2254,25 +2307,25 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="I47:K47"/>
     <mergeCell ref="A15:K15"/>
     <mergeCell ref="A11:K11"/>
-    <mergeCell ref="A49:K49"/>
-    <mergeCell ref="A50:F50"/>
+    <mergeCell ref="G48:H48"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A6:K6"/>
-    <mergeCell ref="A47:F47"/>
     <mergeCell ref="A7:K7"/>
-    <mergeCell ref="A46:K46"/>
+    <mergeCell ref="I48:K48"/>
+    <mergeCell ref="I51:K51"/>
+    <mergeCell ref="A50:K50"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A26:K26"/>
-    <mergeCell ref="I50:K50"/>
     <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A47:K47"/>
+    <mergeCell ref="A48:F48"/>
     <mergeCell ref="A5:K5"/>
     <mergeCell ref="A8:K8"/>
-    <mergeCell ref="G47:H47"/>
+    <mergeCell ref="A51:F51"/>
+    <mergeCell ref="G51:H51"/>
     <mergeCell ref="A10:K10"/>
-    <mergeCell ref="G50:H50"/>
     <mergeCell ref="A9:K9"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>

--- a/КПП/Том СКУД КПП/Журнал входного контроля СКУД КПП.xlsx
+++ b/КПП/Том СКУД КПП/Журнал входного контроля СКУД КПП.xlsx
@@ -1473,7 +1473,7 @@
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>Доводчик дверной</t>
+          <t>Кнопка выхода сенсорная накладная, ST-EX020LSM-BK (поз. BGM)</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="F31" s="10" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G31" s="11" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>Кнопка выхода, ST-EX020LSM-BK / ST-EX241L (поз. BGM)</t>
+          <t>Кнопка выхода металлическая накладная, ST-EX241L (поз. BGM)</t>
         </is>
       </c>
       <c r="D32" s="11" t="inlineStr">

--- a/КПП/Том СКУД КПП/Журнал входного контроля СКУД КПП.xlsx
+++ b/КПП/Том СКУД КПП/Журнал входного контроля СКУД КПП.xlsx
@@ -1266,7 +1266,7 @@
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Болид</t>
         </is>
       </c>
       <c r="E27" s="10" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>НПФ «Витек»</t>
         </is>
       </c>
       <c r="E28" s="10" t="inlineStr">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ALer (ООО «ЭКСКОН»)</t>
         </is>
       </c>
       <c r="E29" s="10" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="D30" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>«Магнито-Контакт»</t>
         </is>
       </c>
       <c r="E30" s="10" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Smartec</t>
         </is>
       </c>
       <c r="E31" s="10" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="D32" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Smartec</t>
         </is>
       </c>
       <c r="E32" s="10" t="inlineStr">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="D34" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Smartec</t>
         </is>
       </c>
       <c r="E34" s="10" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="D38" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>HiWatch</t>
         </is>
       </c>
       <c r="E38" s="10" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>HiWatch</t>
         </is>
       </c>
       <c r="E39" s="10" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="D40" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CHUWI / Acer / DEXP / Defender</t>
         </is>
       </c>
       <c r="E40" s="10" t="inlineStr">
